--- a/output/quickfixclose16_portfolio_daily.xlsx
+++ b/output/quickfixclose16_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5767,20 +5767,68 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
+        <v>228560.5</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>6211.55</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>222348.95</v>
+      </c>
+      <c r="E186" t="n">
+        <v>3</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>228560.5</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>6211.55</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>222348.95</v>
+      </c>
+      <c r="E187" t="n">
+        <v>3</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
         <v>228444.01</v>
       </c>
-      <c r="C186" s="5" t="n">
+      <c r="C188" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D186" s="5" t="n">
+      <c r="D188" s="5" t="n">
         <v>228444.01</v>
       </c>
-      <c r="E186" t="n">
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
         <is>
           <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>

--- a/output/quickfixclose16_portfolio_daily.xlsx
+++ b/output/quickfixclose16_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>228,444.01</t>
+          <t>228,432.02</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+128.44%</t>
+          <t>+128.43%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,907  (7.2 pts of return)</t>
+          <t>3,919  (7.3 pts of return)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5815,22 +5815,78 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>228444.01</v>
+        <v>228560.5</v>
       </c>
       <c r="C188" s="5" t="n">
+        <v>6211.55</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>222348.95</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>228560.5</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>12815.53</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>215744.97</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 2,223); Nasdaq_100_E_mini short (risk 2,201); S_P_500_E_mini short (risk 2,179)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>228432.02</v>
+      </c>
+      <c r="C190" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D188" s="5" t="n">
-        <v>228444.01</v>
-      </c>
-      <c r="E188" t="n">
+      <c r="D190" s="5" t="n">
+        <v>228432.02</v>
+      </c>
+      <c r="E190" t="n">
         <v>0</v>
       </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,157)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9826,9 +9882,181 @@
         <v>-43.42</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>279240.47</v>
+        <v>279220.38</v>
       </c>
       <c r="M78" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>269099.66</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>3740.49</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>-12.99</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>279264.57</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>265359.18</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>3688.49</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>279277.56</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>261670.68</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>3637.22</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>279263.8</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>258033.46</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>3586.67</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>-6.13</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>279277.76</v>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>

--- a/output/quickfixclose16_portfolio_daily.xlsx
+++ b/output/quickfixclose16_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>228,432.02</t>
+          <t>226,249.44</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+128.43%</t>
+          <t>+126.25%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>235,688  (+135.69%)</t>
+          <t>233,463  (+133.46%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,919  (7.3 pts of return)</t>
+          <t>3,944  (7.2 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5.9x</t>
+          <t>5.8x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,335  (-1.28%)</t>
+          <t>-1,349  (-1.27%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5867,26 +5867,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>228432.02</v>
+        <v>228560.5</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>14972.98</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>213587.52</v>
+      </c>
+      <c r="E190" t="n">
+        <v>7</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 2,157)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>226249.44</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>228432.02</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D191" s="5" t="n">
+        <v>226249.44</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 2,157)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 2,136); NY_Palladium_Futures short (risk 2,115)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX stop (-2,172); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5902,7 +5930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9882,7 +9910,7 @@
         <v>-43.42</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>279220.38</v>
+        <v>275592.08</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9925,7 +9953,7 @@
         <v>-12.99</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>279264.57</v>
+        <v>275636.28</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9968,7 +9996,7 @@
         <v>-0.2</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>279277.56</v>
+        <v>275672.5</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -10011,7 +10039,7 @@
         <v>-0.77</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>279263.8</v>
+        <v>275635.51</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -10035,14 +10063,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
+      </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I82" s="5" t="n">
         <v>258033.46</v>
@@ -10051,12 +10087,98 @@
         <v>3586.67</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>-6.13</v>
+        <v>-3611.19</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>279277.76</v>
+        <v>275672.7</v>
       </c>
       <c r="M82" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>254446.8</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>3536.81</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>-9.56</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>275662.94</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>250909.99</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>3487.65</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>-13.68</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>275649.26</v>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
